--- a/sample_teams.xlsx
+++ b/sample_teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yash Mayekar\Projects\MLSC\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652FB923-ABD8-49E4-9764-ECE3F25D030C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7C8AF2-9195-4D64-BFD2-A1C221732E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>teamname</t>
   </si>
@@ -38,6 +38,18 @@
   </si>
   <si>
     <t>https://github.com/l3vith/rag-chatbot</t>
+  </si>
+  <si>
+    <t>https://github.com/YashMayekar/test-repo</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
+    <t>https://github.com/YashMayekar/test2</t>
   </si>
 </sst>
 </file>
@@ -377,14 +389,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -392,19 +404,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/sample_teams.xlsx
+++ b/sample_teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yash Mayekar\Projects\MLSC\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7C8AF2-9195-4D64-BFD2-A1C221732E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836D3604-5E52-496F-8C06-55C3664EA979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>teamname</t>
   </si>
@@ -38,18 +38,6 @@
   </si>
   <si>
     <t>https://github.com/l3vith/rag-chatbot</t>
-  </si>
-  <si>
-    <t>https://github.com/YashMayekar/test-repo</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>xyz</t>
-  </si>
-  <si>
-    <t>https://github.com/YashMayekar/test2</t>
   </si>
 </sst>
 </file>
@@ -389,14 +377,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -404,31 +392,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
         <v>5</v>
       </c>
     </row>
